--- a/Dados/Brutos/pib_sc.xlsx
+++ b/Dados/Brutos/pib_sc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Documents\Projetos Python\proj_munic_sc\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Documents\Projetos Python\proj_munic_sc\Dados\Brutos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDB08F1-D4D5-4DEE-8A56-21817C1CA607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39FF06F-B615-4C9C-9CEF-3220B54C0D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,10 +60,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +77,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,23 +118,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,9 +440,9 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -463,15 +475,15 @@
         <v>2002</v>
       </c>
       <c r="B2" s="3">
-        <v>256231037.93634677</v>
-      </c>
-      <c r="C2" s="3">
+        <v>302425135018.7558</v>
+      </c>
+      <c r="C2" s="4">
         <v>1239639467497.7605</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>14084248131240.508</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>3342778183071.4604</v>
       </c>
       <c r="F2" s="2">
@@ -486,15 +498,15 @@
         <v>2003</v>
       </c>
       <c r="B3" s="3">
-        <v>263122282.96534961</v>
-      </c>
-      <c r="C3" s="3">
+        <v>310558754291.14563</v>
+      </c>
+      <c r="C3" s="4">
         <v>1253781634016.7129</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>14477988212152.773</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>3681006926650.7383</v>
       </c>
       <c r="F3" s="2">
@@ -509,15 +521,15 @@
         <v>2004</v>
       </c>
       <c r="B4" s="3">
-        <v>280445903.46386397</v>
-      </c>
-      <c r="C4" s="3">
+        <v>331005528852.38458</v>
+      </c>
+      <c r="C4" s="4">
         <v>1325999012757.6345</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>15035068144475.613</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>4053944733453.6616</v>
       </c>
       <c r="F4" s="2">
@@ -532,15 +544,15 @@
         <v>2005</v>
       </c>
       <c r="B5" s="3">
-        <v>289754799.25861239</v>
-      </c>
-      <c r="C5" s="3">
+        <v>341992660193.98956</v>
+      </c>
+      <c r="C5" s="4">
         <v>1368459252277.7253</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>15558822251116.695</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>4518455387849.4131</v>
       </c>
       <c r="F5" s="2">
@@ -555,15 +567,15 @@
         <v>2006</v>
       </c>
       <c r="B6" s="3">
-        <v>295396376.43727243</v>
-      </c>
-      <c r="C6" s="3">
+        <v>348651317762.23785</v>
+      </c>
+      <c r="C6" s="4">
         <v>1422677453370.699</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>15992063823932.84</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>5091154930758.4219</v>
       </c>
       <c r="F6" s="2">
@@ -578,15 +590,15 @@
         <v>2007</v>
       </c>
       <c r="B7" s="3">
-        <v>313449360.740255</v>
-      </c>
-      <c r="C7" s="3">
+        <v>369958948013.79706</v>
+      </c>
+      <c r="C7" s="4">
         <v>1509032133942.1814</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>16312522122064.74</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>5811552614974.0908</v>
       </c>
       <c r="F7" s="2">
@@ -601,15 +613,15 @@
         <v>2008</v>
       </c>
       <c r="B8" s="3">
-        <v>319877154.33752149</v>
-      </c>
-      <c r="C8" s="3">
+        <v>377545563445.6441</v>
+      </c>
+      <c r="C8" s="4">
         <v>1585905180197.0039</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>16331051067048.848</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>6373544042638.0059</v>
       </c>
       <c r="F8" s="2">
@@ -624,15 +636,15 @@
         <v>2009</v>
       </c>
       <c r="B9" s="3">
-        <v>317169038.91404712</v>
-      </c>
-      <c r="C9" s="3">
+        <v>374349220882.35931</v>
+      </c>
+      <c r="C9" s="4">
         <v>1583909921137.4202</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>15910281498377.469</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>6972829250985.0967</v>
       </c>
       <c r="F9" s="2">
@@ -647,15 +659,15 @@
         <v>2010</v>
       </c>
       <c r="B10" s="3">
-        <v>338462438.38343114</v>
-      </c>
-      <c r="C10" s="3">
+        <v>399481458028.18292</v>
+      </c>
+      <c r="C10" s="4">
         <v>1703150236756.7844</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>16339094225152.506</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>7711689202853.2861</v>
       </c>
       <c r="F10" s="2">
@@ -670,15 +682,15 @@
         <v>2011</v>
       </c>
       <c r="B11" s="3">
-        <v>351604546.1190092</v>
-      </c>
-      <c r="C11" s="3">
+        <v>414992864212.12268</v>
+      </c>
+      <c r="C11" s="4">
         <v>1770840632844.1025</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>16594704135316.656</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>8441318020902.4248</v>
       </c>
       <c r="F11" s="2">
@@ -693,15 +705,15 @@
         <v>2012</v>
       </c>
       <c r="B12" s="3">
-        <v>356333639.40232944</v>
-      </c>
-      <c r="C12" s="3">
+        <v>420574532562.07416</v>
+      </c>
+      <c r="C12" s="4">
         <v>1804861597828.479</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>16974575729098.225</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>9104482675356.3574</v>
       </c>
       <c r="F12" s="2">
@@ -716,15 +728,15 @@
         <v>2013</v>
       </c>
       <c r="B13" s="3">
-        <v>369216283.71204519</v>
-      </c>
-      <c r="C13" s="3">
+        <v>435779698478.51617</v>
+      </c>
+      <c r="C13" s="4">
         <v>1859094488272.1243</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>17334068402873.9</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <v>9812695262900.8906</v>
       </c>
       <c r="F13" s="2">
@@ -739,15 +751,15 @@
         <v>2014</v>
       </c>
       <c r="B14" s="3">
-        <v>377513144.94106877</v>
-      </c>
-      <c r="C14" s="3">
+        <v>445572342639.14569</v>
+      </c>
+      <c r="C14" s="4">
         <v>1868463501662.2988</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>17771549055750.484</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <v>10544908798423.977</v>
       </c>
       <c r="F14" s="2">
@@ -762,15 +774,15 @@
         <v>2015</v>
       </c>
       <c r="B15" s="3">
-        <v>364570542.70007032</v>
-      </c>
-      <c r="C15" s="3">
+        <v>430296409396.42731</v>
+      </c>
+      <c r="C15" s="4">
         <v>1802212206814.5039</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>18295019000000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <v>11280814787468.914</v>
       </c>
       <c r="F15" s="2">
@@ -785,15 +797,15 @@
         <v>2016</v>
       </c>
       <c r="B16" s="3">
-        <v>356953884.51163483</v>
-      </c>
-      <c r="C16" s="3">
+        <v>421306597312.84381</v>
+      </c>
+      <c r="C16" s="4">
         <v>1743173232416.637</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>18627887993267.523</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <v>12045152668727.279</v>
       </c>
       <c r="F16" s="2">
@@ -808,15 +820,15 @@
         <v>2017</v>
       </c>
       <c r="B17" s="3">
-        <v>372048387.7739929</v>
-      </c>
-      <c r="C17" s="3">
+        <v>439122382722.46997</v>
+      </c>
+      <c r="C17" s="4">
         <v>1766233131666.655</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>19085691122935.238</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>12875216222853.414</v>
       </c>
       <c r="F17" s="2">
@@ -831,15 +843,15 @@
         <v>2018</v>
       </c>
       <c r="B18" s="3">
-        <v>390626315.72377366</v>
-      </c>
-      <c r="C18" s="3">
+        <v>461049595029.89117</v>
+      </c>
+      <c r="C18" s="4">
         <v>1797736844969.1604</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>19651869117582.469</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <v>13745158275136.672</v>
       </c>
       <c r="F18" s="2">
@@ -854,15 +866,15 @@
         <v>2019</v>
       </c>
       <c r="B19" s="3">
-        <v>405097780.97925496</v>
-      </c>
-      <c r="C19" s="3">
+        <v>478130019279.2569</v>
+      </c>
+      <c r="C19" s="4">
         <v>1819683217699.3813</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="4">
         <v>20159639089698.133</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="4">
         <v>14579283528148.377</v>
       </c>
       <c r="F19" s="2">
@@ -877,15 +889,15 @@
         <v>2020</v>
       </c>
       <c r="B20" s="3">
-        <v>394913750.48807448</v>
-      </c>
-      <c r="C20" s="3">
+        <v>466109981343.43335</v>
+      </c>
+      <c r="C20" s="4">
         <v>1760056587795.4631</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>19723580221938.238</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>14920466234565.322</v>
       </c>
       <c r="F20" s="2">
@@ -900,15 +912,15 @@
         <v>2021</v>
       </c>
       <c r="B21" s="3">
-        <v>428570883</v>
-      </c>
-      <c r="C21" s="3">
+        <v>505834938788.84491</v>
+      </c>
+      <c r="C21" s="4">
         <v>1843881119920.2031</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>20917853444668.305</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>16199162892908.637</v>
       </c>
       <c r="F21" s="2">
@@ -923,15 +935,15 @@
         <v>2022</v>
       </c>
       <c r="B22" s="3">
-        <v>437324665.04532391</v>
-      </c>
-      <c r="C22" s="3">
+        <v>510853581829.61658</v>
+      </c>
+      <c r="C22" s="4">
         <v>1899505377558.02</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>21443388432051.027</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="4">
         <v>16706875253648.482</v>
       </c>
       <c r="F22" s="2">
@@ -946,15 +958,15 @@
         <v>2023</v>
       </c>
       <c r="B23" s="3">
-        <v>447794946.40095067</v>
-      </c>
-      <c r="C23" s="3">
+        <v>513392972000</v>
+      </c>
+      <c r="C23" s="4">
         <v>1961080794855.5972</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>22062578283266.758</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="4">
         <v>17611526369126.551</v>
       </c>
       <c r="F23" s="2">
@@ -968,16 +980,17 @@
       <c r="A24" s="1">
         <v>2024</v>
       </c>
-      <c r="B24" s="3">
-        <v>472930181.52443063</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B24" s="4">
+        <f>B23+B23*0.056</f>
+        <v>542142978432</v>
+      </c>
+      <c r="C24" s="4">
         <v>2027676479714.6897</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>22679489969555.609</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <v>18488114837769.328</v>
       </c>
       <c r="F24" s="2">

--- a/Dados/Brutos/pib_sc.xlsx
+++ b/Dados/Brutos/pib_sc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Documents\Projetos Python\proj_munic_sc\Dados\Brutos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Desktop\proj_munic_sc\Dados\Brutos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39FF06F-B615-4C9C-9CEF-3220B54C0D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2F458F-5E07-470E-8317-3F8CCB95A697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -130,8 +130,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -958,7 +958,7 @@
         <v>2023</v>
       </c>
       <c r="B23" s="3">
-        <v>513392972000</v>
+        <v>527187560295.20911</v>
       </c>
       <c r="C23" s="4">
         <v>1961080794855.5972</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="B24" s="4">
         <f>B23+B23*0.056</f>
-        <v>542142978432</v>
+        <v>556710063671.74084</v>
       </c>
       <c r="C24" s="4">
         <v>2027676479714.6897</v>
